--- a/Отчет_по_товарам_за_период_2025_11_24_2025_11_30.xlsx
+++ b/Отчет_по_товарам_за_период_2025_11_24_2025_11_30.xlsx
@@ -1160,12 +1160,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1239,7 +1240,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1265,6 +1266,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1391,7 +1396,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y236"/>
+  <dimension ref="A1:AG236"/>
   <sheetFormatPr defaultColWidth="8.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.22"/>
@@ -1637,6 +1642,21 @@
       <c r="Y3" s="5" t="n">
         <v>1247.22</v>
       </c>
+      <c r="AD3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="7" t="n">
+        <f aca="false">AD3/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF3" s="7" t="n">
+        <f aca="false">AE3*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG3" s="7" t="n">
+        <f aca="false">AD3+AF3</f>
+        <v>1.54545454545455</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
@@ -1710,6 +1730,21 @@
       <c r="Y4" s="5" t="n">
         <v>364.98</v>
       </c>
+      <c r="AD4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="7" t="n">
+        <f aca="false">AD4/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF4" s="7" t="n">
+        <f aca="false">AE4*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG4" s="7" t="n">
+        <f aca="false">AD4+AF4</f>
+        <v>1.54545454545455</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
@@ -1780,8 +1815,23 @@
       <c r="Y5" s="5" t="n">
         <v>-11.94</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AD5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" s="7" t="n">
+        <f aca="false">AD5/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF5" s="7" t="n">
+        <f aca="false">AE5*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG5" s="7" t="n">
+        <f aca="false">AD5+AF5</f>
+        <v>1.54545454545455</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>45987</v>
       </c>
@@ -1850,8 +1900,23 @@
       <c r="Y6" s="5" t="n">
         <v>-7.26</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AD6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" s="7" t="n">
+        <f aca="false">AD6/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF6" s="7" t="n">
+        <f aca="false">AE6*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG6" s="7" t="n">
+        <f aca="false">AD6+AF6</f>
+        <v>1.54545454545455</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="9.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>45987</v>
       </c>
@@ -1920,6 +1985,21 @@
       <c r="Y7" s="5" t="n">
         <v>-24.94</v>
       </c>
+      <c r="AD7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="7" t="n">
+        <f aca="false">AD7/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF7" s="7" t="n">
+        <f aca="false">AE7*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG7" s="7" t="n">
+        <f aca="false">AD7+AF7</f>
+        <v>1.54545454545455</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
@@ -1993,6 +2073,21 @@
       <c r="Y8" s="5" t="n">
         <v>1218.3</v>
       </c>
+      <c r="AD8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="7" t="n">
+        <f aca="false">AD8/$AD$10</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="AF8" s="7" t="n">
+        <f aca="false">AE8*$AD$11</f>
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AG8" s="7" t="n">
+        <f aca="false">AD8+AF8</f>
+        <v>1.54545454545455</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
@@ -2065,6 +2160,21 @@
       </c>
       <c r="Y9" s="5" t="n">
         <v>-133.7</v>
+      </c>
+      <c r="AD9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="7" t="n">
+        <f aca="false">AD9/$AD$10</f>
+        <v>0.454545454545455</v>
+      </c>
+      <c r="AF9" s="7" t="n">
+        <f aca="false">AE9*$AD$11</f>
+        <v>-2.27272727272727</v>
+      </c>
+      <c r="AG9" s="7" t="n">
+        <f aca="false">AD9+AF9</f>
+        <v>7.72727272727273</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2139,6 +2249,22 @@
       <c r="Y10" s="5" t="n">
         <v>-56</v>
       </c>
+      <c r="AD10" s="7" t="n">
+        <f aca="false">AD9+AD8+AD7+AD6+AD5+AD4+AD3</f>
+        <v>22</v>
+      </c>
+      <c r="AE10" s="7" t="n">
+        <f aca="false">AE9+AE8+AE7+AE6+AE5+AE4+AE3</f>
+        <v>1</v>
+      </c>
+      <c r="AF10" s="7" t="n">
+        <f aca="false">AF9+AF8+AF7+AF6+AF5+AF4+AF3</f>
+        <v>-5</v>
+      </c>
+      <c r="AG10" s="7" t="n">
+        <f aca="false">AG9+AG8+AG7+AG6+AG5+AG4+AG3</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
@@ -2211,6 +2337,9 @@
       </c>
       <c r="Y11" s="5" t="n">
         <v>474.68</v>
+      </c>
+      <c r="AD11" s="0" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9162,7 +9291,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="n">
         <v>45989</v>
       </c>
